--- a/src/Excelsior.Tests/RowHeights.MaxRowHeightFluent.verified.xlsx
+++ b/src/Excelsior.Tests/RowHeights.MaxRowHeightFluent.verified.xlsx
@@ -130,10 +130,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="A2:A4">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="This field is required." sqref="A2:A4">
       <formula1>LEN(TRIM(A2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B4">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="This field is required." sqref="B2:B4">
       <formula1>LEN(TRIM(B2))&gt;0</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/RowHeights.MaxRowHeightFluent.verified.xlsx
+++ b/src/Excelsior.Tests/RowHeights.MaxRowHeightFluent.verified.xlsx
@@ -130,10 +130,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="This field is required." sqref="A2:A4">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="A2:A4">
       <formula1>LEN(TRIM(A2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="This field is required." sqref="B2:B4">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="B2:B4">
       <formula1>LEN(TRIM(B2))&gt;0</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/RowHeights.MaxRowHeightFluent.verified.xlsx
+++ b/src/Excelsior.Tests/RowHeights.MaxRowHeightFluent.verified.xlsx
@@ -130,10 +130,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="A2:A4">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="A2:A4">
       <formula1>LEN(TRIM(A2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B4">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="B2:B4">
       <formula1>LEN(TRIM(B2))&gt;0</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/RowHeights.MaxRowHeightFluent.verified.xlsx
+++ b/src/Excelsior.Tests/RowHeights.MaxRowHeightFluent.verified.xlsx
@@ -141,7 +141,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Title"/>
     <column index="2" property="Body"/>
